--- a/TDD_examples/CASE_3_HTS_HVDC/transitory_input.xlsx
+++ b/TDD_examples/CASE_3_HTS_HVDC/transitory_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politoit-my.sharepoint.com/personal/daniele_placido_polito_it/Documents/OPENSC2/Description_of_Components/HTS_best_paths/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politoit-my.sharepoint.com/personal/daniele_placido_polito_it/Documents/MAHTEP/OPENSC2_work/year_2024/adaptivity/Adaptive_time_step/input_files/CASE_3_HTS_HVDC_test_adapt_tstep/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{8A1A4B2A-21A8-4A23-BF39-C5996AD9CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C54B443-959E-4B67-9200-AA11BA5FFAE2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5C17BCB8-4C66-4750-9BEE-3F59E6778707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7E29C0-2D67-4AEC-84A1-7BCA0510F72E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRANSIENT" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>SIMULATION</t>
   </si>
@@ -47,9 +47,6 @@
     <t>s</t>
   </si>
   <si>
-    <t>![s] real(ncond) - simulation end time</t>
-  </si>
-  <si>
     <t>IADAPTIME</t>
   </si>
   <si>
@@ -101,21 +98,12 @@
     <t>file to define each conductor</t>
   </si>
   <si>
-    <t>flag for time adaptivity: 0 = no adaptivity (tstep=tstepmin); 1 = adaptivity on</t>
-  </si>
-  <si>
-    <t>minimum timestep</t>
-  </si>
-  <si>
     <t>time when the most refined time step is adopted</t>
   </si>
   <si>
     <t>time duration of the most time refined grid, starting STPMAX2 seconds before TIMEREF (era TAUDUM in origine)</t>
   </si>
   <si>
-    <t>maximum timestep</t>
-  </si>
-  <si>
     <t>STPMAX</t>
   </si>
   <si>
@@ -129,6 +117,39 @@
   </si>
   <si>
     <t>environment_input.xlsx</t>
+  </si>
+  <si>
+    <t>End time of the simulation</t>
+  </si>
+  <si>
+    <t>Flag for time adaptivity: 0 = no adaptivity (tstep=tstepmin); 1 = adaptivity based on variation of the whole thermal-hydraulic solution; 2 = adaptivity based only on temperature variation of the thermal-hydraulic solution; -1 = adaptive time step from user defined input file (to be implemented); -2 = adaptive time step from user defined function.</t>
+  </si>
+  <si>
+    <t>Minimum time step for the thermal-hydraulic loop. Used if flag IADAPTIME = 0. Lower bound of the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2</t>
+  </si>
+  <si>
+    <t>Maximum time step for the thermal-hydraulic loop. It is the Upper bound of the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2</t>
+  </si>
+  <si>
+    <t>float or str</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplier used to tune (increase) the adaptive time step, used if flag IADAPTIME = 1 or IADAPTIME = 2; default to 1.2. Any positive real number or none. If none default value is used. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplier used to tune (decrease) the adaptive time step, used if flag IADAPTIME = 1 or IADAPTIME = 2; default to 0.5. Any positive real number or none. If none default value is used. </t>
+  </si>
+  <si>
+    <t>MLT_INCREASE</t>
+  </si>
+  <si>
+    <t>MLT_DECREASE</t>
+  </si>
+  <si>
+    <t>TIME_STEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User defined time step for the thermal-hydraulic loop. Should be in the range [STPMIN, STPMAX] (boundary included). </t>
   </si>
 </sst>
 </file>
@@ -186,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -207,18 +228,30 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -239,13 +272,16 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="GRID"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="4">
           <cell r="A4" t="str">
             <v>NELEMS</v>
@@ -261,9 +297,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -301,7 +337,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -407,7 +443,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -549,7 +585,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -557,39 +593,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6328125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="95.81640625" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.90625" style="3"/>
+    <col min="7" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -597,51 +633,51 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="8" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,A6,E6,A8,E8,[1]GRID!$A$4,[1]GRID!$E$4)</f>
-        <v>TEND_20000_STPMIN_10_NELEMS_200</v>
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A6,E6,A9,E9,[1]GRID!$A$4,[1]GRID!$E$4,"case3_test_adapt_time_20240416")</f>
+        <v>TEND_20000_STPMIN_10_NELEMS_200_case3_test_adapt_time_20240416</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -652,102 +688,153 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="8">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="D7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="E14" s="10">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="9">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
